--- a/output/pdf_financials_xlsx/AMM.xlsx
+++ b/output/pdf_financials_xlsx/AMM.xlsx
@@ -6720,37 +6720,37 @@
         <v>4.685764</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>5.735249</v>
+        <v>3.327114</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.010251</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.861644</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>9.947336</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.005757</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>11.822637</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>11.822637</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>13.552101</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>15.528276</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>16.706832</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>17.689952</v>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>21.068273</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>22.546373</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>23.356523</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>23.356523</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>23.418523</v>
       </c>
     </row>
     <row r="93">
@@ -11501,7 +11501,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -13772,7 +13776,11 @@
           <t>Reserves (Note 10) 23,356,523</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -15728,7 +15736,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -16491,7 +16503,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -17470,7 +17486,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -19238,7 +19258,11 @@
           <t>Reserves (Note 13)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -20736,7 +20760,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -29334,7 +29362,11 @@
           <t>Reserves (Note 10) 7,010,251</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AMM.xlsx
+++ b/output/pdf_financials_xlsx/AMM.xlsx
@@ -1089,52 +1089,52 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.622668</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.372107</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.169458</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.038589</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.161664</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.173302</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.165474</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.175955</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.073279</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.154943</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.164435</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.04165</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.040196</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.490245</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.253869</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2128,18 +2128,14 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>44.214511</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>45.007101</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>45.71918</v>
+        <v>45.846627</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>49.495029</v>
@@ -2235,46 +2231,46 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.425687</v>
+        <v>-2.595145</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.770418</v>
+        <v>-3.809007</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.274858</v>
+        <v>7.113194</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-10.238377</v>
+        <v>-10.411679</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.356609</v>
+        <v>-6.522083</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-13.143185</v>
+        <v>-13.31914</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.549125</v>
+        <v>-1.622404</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-4.023504</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.231295</v>
+        <v>-5.386238</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.511667</v>
+        <v>-3.676102</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.73077</v>
+        <v>-3.77242</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.107888</v>
+        <v>-3.148084</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.340783</v>
+        <v>-2.831028</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.457996</v>
+        <v>-10.711865</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-66.67093800000001</v>
@@ -2367,46 +2363,46 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.255714</v>
+        <v>-2.425172</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.580838</v>
+        <v>-3.619427</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.545919</v>
+        <v>7.384255</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.912381999999999</v>
+        <v>-10.085684</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.053219</v>
+        <v>-6.218693</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-12.897546</v>
+        <v>-13.073501</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.417639</v>
+        <v>-1.490918</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-3.996465</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.203021</v>
+        <v>-5.357964</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.48339</v>
+        <v>-3.647825</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.706571</v>
+        <v>-3.748221</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.088324</v>
+        <v>-3.12852</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.324145</v>
+        <v>-2.81439</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.443572</v>
+        <v>-10.697441</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-66.659772</v>
@@ -2435,25 +2431,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-92.42384821227729</v>
+        <v>-99.36708679232605</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1531.090539818279</v>
+        <v>-1547.590379476216</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3033.998761619865</v>
+        <v>2968.998279134099</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-3313.327338911043</v>
+        <v>-3371.255519492458</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-2746.07089714742</v>
+        <v>-2821.138945343689</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-5077.953943249958</v>
+        <v>-5147.230019961337</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-467.246203893831</v>
+        <v>-491.3985689001098</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -18372,7 +18368,11 @@
           <t>Reclamation deposit (Note 4(m))</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -20118,7 +20118,11 @@
           <t>Reclamation deposit (Note 3(m))</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -24046,7 +24050,11 @@
           <t>Reclamation deposit (Note 3(l))</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -27130,7 +27138,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -28135,7 +28147,11 @@
           <t>Reclamation deposit 124,764</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -30932,7 +30948,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -45170,7 +45190,11 @@
           <t>Unrealized foreign exchange on reclamation deposit</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -45723,7 +45747,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -68065,7 +68093,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -75158,7 +75186,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -82728,7 +82756,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E675" s="5" t="n">
@@ -84890,7 +84918,7 @@
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E695" s="5" t="n">

--- a/output/pdf_financials_xlsx/AMM.xlsx
+++ b/output/pdf_financials_xlsx/AMM.xlsx
@@ -790,40 +790,40 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.282585</v>
+        <v>0.330585</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.277615</v>
+        <v>0.325615</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.230628</v>
+        <v>0.271628</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.208346</v>
+        <v>0.278346</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.238815</v>
+        <v>0.308815</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.066096</v>
+        <v>0.136096</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.075568</v>
+        <v>0.145568</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.089476</v>
+        <v>0.191976</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.096068</v>
+        <v>0.241068</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.103491</v>
+        <v>0.243491</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.103491</v>
+        <v>0.243491</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.104456</v>
+        <v>0.224456</v>
       </c>
     </row>
     <row r="8">
@@ -1413,19 +1413,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.238151</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.139728</v>
+        <v>-0.139728</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.305766</v>
+        <v>-0.305766</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1437,7 +1437,7 @@
         <v>1.839482</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.4046</v>
+        <v>-0.4046</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1461,10 +1461,10 @@
         <v>1.341185</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>3.090208</v>
+        <v>-3.090208</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>3.090208</v>
+        <v>-3.090208</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>-0</v>
@@ -8163,16 +8163,16 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.579783</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>4.435757</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.022565</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.039343</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -41159,7 +41159,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -43123,7 +43127,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -44976,7 +44984,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -48642,7 +48654,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -59701,7 +59717,11 @@
           <t>Directors’ fees (Note 11(a)) 52,500</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -61423,7 +61443,11 @@
           <t>Deferred income tax recovery (expense) (Note 14) -</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -62983,7 +63007,11 @@
           <t>Directors’ fees (Note 11(a)) 120,000</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -65995,7 +66023,11 @@
           <t>Directors’ fees (Note 11(a))</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -67471,7 +67503,11 @@
           <t>Deferred income tax recovery (expense) (Note 14)</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr"/>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
@@ -69403,7 +69439,11 @@
           <t>Directors’ fees (Note 10(a))</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -70279,7 +70319,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -71038,7 +71082,11 @@
           <t>Directors’ fees (Note 9(a))</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr"/>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E567" t="inlineStr">
         <is>
           <t>-</t>
@@ -71583,7 +71631,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr"/>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
@@ -72235,7 +72287,11 @@
           <t>Directors’ fees (Note 13(a))</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
@@ -73539,7 +73595,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr"/>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E590" t="inlineStr">
         <is>
           <t>-</t>
@@ -74635,7 +74695,11 @@
           <t>Deferred income tax recovery (expense) (Note 17)</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -77203,7 +77267,11 @@
           <t>Deferred income tax recovery (expense) (Note 18)</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E624" t="inlineStr">
         <is>
           <t>-</t>
@@ -80675,7 +80743,11 @@
           <t>Income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr"/>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E656" t="inlineStr">
         <is>
           <t>-</t>
@@ -82205,7 +82277,11 @@
           <t>Income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E670" t="inlineStr">
         <is>
           <t>-</t>
@@ -84591,7 +84667,11 @@
           <t>Income tax recovery (Note 14) 1,754,119</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E692" s="5" t="n">
         <v>0.6425999999999999</v>
       </c>
